--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:46:32+00:00</t>
+    <t>2024-11-16T15:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:52:33+00:00</t>
+    <t>2024-11-16T16:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T16:02:40+00:00</t>
+    <t>2025-01-17T11:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
